--- a/feasibility_outputs/profile_final_write_plan_draft/final_write_plan_review.xlsx
+++ b/feasibility_outputs/profile_final_write_plan_draft/final_write_plan_review.xlsx
@@ -14,9 +14,9 @@
     <sheet name="Source Trace" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Final Write Plan'!$A$1:$L$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blocked Items'!$A$1:$L$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Risk Register'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Final Write Plan'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Blocked Items'!$A$1:$L$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Risk Register'!$A$1:$F$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Source Trace'!$A$1:$K$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -65,8 +65,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-        <bgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2EFDA"/>
+        <bgColor rgb="00E2EFDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -100,7 +100,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -112,14 +112,14 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -490,7 +490,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="27" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -513,7 +513,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>FINAL_WRITE_PLAN_BLOCKED</t>
+          <t>FINAL_WRITE_PLAN_READY_FOR_HUMAN_REVIEW</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -653,6 +653,265 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>final_plan_item_id</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>write_candidate_id</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>supplier_code</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>material_code</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>quantity</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>unit_price</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>final_planned_action</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>action_source</t>
+        </is>
+      </c>
+      <c r="L1" s="5" t="inlineStr">
+        <is>
+          <t>risk_level</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_ITEM_0001</t>
+        </is>
+      </c>
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0001</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>CHINT</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>NXM-63S</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>MCCB Chint NXM-63S 3P 25÷63 25</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>800000</v>
+      </c>
+      <c r="J2" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_INSERT</t>
+        </is>
+      </c>
+      <c r="K2" s="7" t="inlineStr">
+        <is>
+          <t>master_match</t>
+        </is>
+      </c>
+      <c r="L2" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_ITEM_0002</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0002</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>CHINT</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>NXM-125S</t>
+        </is>
+      </c>
+      <c r="E3" s="7" t="inlineStr">
+        <is>
+          <t>MCCB Chint NXM-125S 3P 80÷125 25</t>
+        </is>
+      </c>
+      <c r="F3" s="7" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>860000</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>860000</v>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_INSERT</t>
+        </is>
+      </c>
+      <c r="K3" s="7" t="inlineStr">
+        <is>
+          <t>master_match</t>
+        </is>
+      </c>
+      <c r="L3" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_ITEM_0003</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>WRITE_CANDIDATE_0003</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>CHINT</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>NXM-250S</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>MCCB Chint NXM-250S 3P 160,200,250 35</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>cái</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="I4" s="8" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="J4" s="6" t="inlineStr">
+        <is>
+          <t>PLAN_INSERT</t>
+        </is>
+      </c>
+      <c r="K4" s="7" t="inlineStr">
+        <is>
+          <t>master_match</t>
+        </is>
+      </c>
+      <c r="L4" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -743,279 +1002,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="23" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>final_plan_item_id</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>write_candidate_id</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>supplier_code</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>material_code</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>unit</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>quantity</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>unit_price</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>amount</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>final_planned_action</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>action_source</t>
-        </is>
-      </c>
-      <c r="L1" s="5" t="inlineStr">
-        <is>
-          <t>risk_level</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_ITEM_0001</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>WRITE_CANDIDATE_0001</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>NXM-63S</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>MCCB Chint NXM-63S 3P 25÷63 25</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" s="7" t="n">
-        <v>800000</v>
-      </c>
-      <c r="I2" s="7" t="n">
-        <v>800000</v>
-      </c>
-      <c r="J2" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_BLOCKED</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>default_blocked</t>
-        </is>
-      </c>
-      <c r="L2" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_ITEM_0002</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>WRITE_CANDIDATE_0002</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>NXM-125S</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>MCCB Chint NXM-125S 3P 80÷125 25</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>860000</v>
-      </c>
-      <c r="I3" s="7" t="n">
-        <v>860000</v>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_BLOCKED</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>default_blocked</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_ITEM_0003</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>WRITE_CANDIDATE_0003</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>CHINT</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>NXM-250S</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>MCCB Chint NXM-250S 3P 160,200,250 35</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>cái</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" s="7" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="I4" s="7" t="n">
-        <v>1400000</v>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_BLOCKED</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>default_blocked</t>
-        </is>
-      </c>
-      <c r="L4" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:L4"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="21" customWidth="1" min="2" max="2"/>
     <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -1051,98 +1051,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>RISK_0001</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_ITEM_0001</t>
-        </is>
-      </c>
-      <c r="C2" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>Bản ghi bị chặn ở khâu lập kế hoạch.</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Reviewer mở tệp Excel Resolution phân xử thủ công dòng này.</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
-          <t>RISK_0002</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_ITEM_0002</t>
-        </is>
-      </c>
-      <c r="C3" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Bản ghi bị chặn ở khâu lập kế hoạch.</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>Reviewer mở tệp Excel Resolution phân xử thủ công dòng này.</t>
-        </is>
-      </c>
-      <c r="F3" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>RISK_0003</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>PLAN_ITEM_0003</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Bản ghi bị chặn ở khâu lập kế hoạch.</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Reviewer mở tệp Excel Resolution phân xử thủ công dòng này.</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1227,111 +1137,135 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>PLAN_ITEM_0001</t>
         </is>
       </c>
-      <c r="B2" s="8" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>WRITE_CANDIDATE_0001</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>SIM_REC_0001</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>MATCH_RES_0001</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="n"/>
+      <c r="F2" s="9" t="inlineStr">
         <is>
           <t>CHINT</t>
         </is>
       </c>
-      <c r="G2" s="8" t="inlineStr">
+      <c r="G2" s="9" t="inlineStr">
         <is>
           <t>NXM-63S</t>
         </is>
       </c>
-      <c r="H2" s="9" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t>CHINT|NXM-63S|P3|800000|MCCBCHINTNXM63S3P256325</t>
         </is>
       </c>
-      <c r="I2" s="8" t="n"/>
-      <c r="J2" s="8" t="n"/>
-      <c r="K2" s="9" t="inlineStr">
+      <c r="I2" s="9" t="n"/>
+      <c r="J2" s="9" t="n"/>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>Source PDF: Bảng giá Chint 1-3-2023 ck 50.pdf, Page: 3, Layout: chint_mccb_nxm_nm1, Method: coordinate_column_profiler</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="8" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>PLAN_ITEM_0002</t>
         </is>
       </c>
-      <c r="B3" s="8" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>WRITE_CANDIDATE_0002</t>
         </is>
       </c>
-      <c r="C3" s="8" t="n"/>
-      <c r="D3" s="8" t="n"/>
-      <c r="E3" s="8" t="n"/>
-      <c r="F3" s="8" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>SIM_REC_0002</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="inlineStr">
+        <is>
+          <t>MATCH_RES_0002</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t>CHINT</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="9" t="inlineStr">
         <is>
           <t>NXM-125S</t>
         </is>
       </c>
-      <c r="H3" s="9" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>CHINT|NXM-125S|P3|860000|MCCBCHINTNXM125S3P801252</t>
         </is>
       </c>
-      <c r="I3" s="8" t="n"/>
-      <c r="J3" s="8" t="n"/>
-      <c r="K3" s="9" t="inlineStr">
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>Source PDF: Bảng giá Chint 1-3-2023 ck 50.pdf, Page: 3, Layout: chint_mccb_nxm_nm1, Method: coordinate_column_profiler</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>PLAN_ITEM_0003</t>
         </is>
       </c>
-      <c r="B4" s="8" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>WRITE_CANDIDATE_0003</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n"/>
-      <c r="D4" s="8" t="n"/>
-      <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>SIM_REC_0003</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="inlineStr">
+        <is>
+          <t>MATCH_RES_0003</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t>CHINT</t>
         </is>
       </c>
-      <c r="G4" s="8" t="inlineStr">
+      <c r="G4" s="9" t="inlineStr">
         <is>
           <t>NXM-250S</t>
         </is>
       </c>
-      <c r="H4" s="9" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>CHINT|NXM-250S|P3|1400000|MCCBCHINTNXM250S3P160200</t>
         </is>
       </c>
-      <c r="I4" s="8" t="n"/>
-      <c r="J4" s="8" t="n"/>
-      <c r="K4" s="9" t="inlineStr">
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>Source PDF: Bảng giá Chint 1-3-2023 ck 50.pdf, Page: 3, Layout: chint_mccb_nxm_nm1, Method: coordinate_column_profiler</t>
         </is>
